--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_LIMITED_ENTRY_MATUREBULL_PRIVATE_LANDS.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_LIMITED_ENTRY_MATUREBULL_PRIVATE_LANDS.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:M134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -531,6 +531,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -584,10 +585,15 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -640,8 +646,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -690,8 +701,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr"/>
-      <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -736,8 +752,13 @@
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -782,8 +803,13 @@
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
-      <c r="L7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -828,8 +854,13 @@
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -874,8 +905,13 @@
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
-      <c r="L9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -920,8 +956,13 @@
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -966,8 +1007,13 @@
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr"/>
-      <c r="K11" s="6" t="inlineStr"/>
-      <c r="L11" s="6" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -1012,8 +1058,13 @@
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1058,8 +1109,13 @@
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
-      <c r="L13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1104,8 +1160,13 @@
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1150,8 +1211,13 @@
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -1196,8 +1262,13 @@
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1242,8 +1313,13 @@
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr"/>
-      <c r="K17" s="6" t="inlineStr"/>
-      <c r="L17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -1292,8 +1368,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1346,8 +1427,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr"/>
-      <c r="L19" s="6" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1396,8 +1482,13 @@
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1442,8 +1533,13 @@
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
-      <c r="L21" s="6" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -1488,8 +1584,13 @@
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -1534,8 +1635,13 @@
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr"/>
-      <c r="K23" s="6" t="inlineStr"/>
-      <c r="L23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -1584,8 +1690,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1634,8 +1745,13 @@
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
-      <c r="L25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -1680,8 +1796,13 @@
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -1730,8 +1851,13 @@
           <t>40</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr"/>
-      <c r="L27" s="6" t="inlineStr">
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -1784,8 +1910,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1834,8 +1965,13 @@
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr"/>
-      <c r="K29" s="6" t="inlineStr"/>
-      <c r="L29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -1880,8 +2016,13 @@
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -1926,8 +2067,13 @@
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
-      <c r="L31" s="6" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="6" t="inlineStr"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -1972,8 +2118,13 @@
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -2018,8 +2169,13 @@
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
-      <c r="L33" s="6" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="6" t="inlineStr"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -2064,8 +2220,13 @@
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -2114,8 +2275,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K35" s="6" t="inlineStr"/>
-      <c r="L35" s="6" t="inlineStr">
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2164,8 +2330,13 @@
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr"/>
-      <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -2210,8 +2381,13 @@
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr"/>
-      <c r="K37" s="6" t="inlineStr"/>
-      <c r="L37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="6" t="inlineStr"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
@@ -2256,8 +2432,13 @@
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr"/>
-      <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="4" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -2302,8 +2483,13 @@
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr"/>
-      <c r="K39" s="6" t="inlineStr"/>
-      <c r="L39" s="6" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="6" t="inlineStr"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -2352,8 +2538,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2402,8 +2593,13 @@
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr"/>
-      <c r="K41" s="6" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="6" t="inlineStr"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
@@ -2448,8 +2644,13 @@
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -2498,8 +2699,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K43" s="6" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2552,8 +2758,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2602,8 +2813,13 @@
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr"/>
-      <c r="K45" s="6" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="6" t="inlineStr"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
@@ -2652,8 +2868,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2702,8 +2923,13 @@
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr"/>
-      <c r="K47" s="6" t="inlineStr"/>
-      <c r="L47" s="6" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="6" t="inlineStr"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
@@ -2752,8 +2978,13 @@
           <t>57.1</t>
         </is>
       </c>
-      <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -2802,8 +3033,13 @@
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr"/>
-      <c r="K49" s="6" t="inlineStr"/>
-      <c r="L49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="6" t="inlineStr"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
@@ -2848,8 +3084,13 @@
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr"/>
-      <c r="K50" s="4" t="inlineStr"/>
-      <c r="L50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -2894,8 +3135,13 @@
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr"/>
-      <c r="K51" s="6" t="inlineStr"/>
-      <c r="L51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="6" t="inlineStr"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
@@ -2940,8 +3186,13 @@
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr"/>
-      <c r="K52" s="4" t="inlineStr"/>
-      <c r="L52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -2986,8 +3237,13 @@
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr"/>
-      <c r="K53" s="6" t="inlineStr"/>
-      <c r="L53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
@@ -3036,8 +3292,13 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -3086,8 +3347,13 @@
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr"/>
-      <c r="K55" s="6" t="inlineStr"/>
-      <c r="L55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="6" t="inlineStr"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
@@ -3132,8 +3398,13 @@
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr"/>
-      <c r="K56" s="4" t="inlineStr"/>
-      <c r="L56" s="4" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="4" t="inlineStr"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -3178,8 +3449,13 @@
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr"/>
-      <c r="K57" s="6" t="inlineStr"/>
-      <c r="L57" s="6" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="6" t="inlineStr"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
@@ -3224,8 +3500,13 @@
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr"/>
-      <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr"/>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -3270,8 +3551,13 @@
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr"/>
-      <c r="K59" s="6" t="inlineStr"/>
-      <c r="L59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="6" t="inlineStr"/>
     </row>
     <row r="60" ht="32" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
@@ -3316,8 +3602,13 @@
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr"/>
-      <c r="K60" s="4" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="4" t="inlineStr"/>
     </row>
     <row r="61" ht="32" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -3362,8 +3653,13 @@
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr"/>
-      <c r="K61" s="6" t="inlineStr"/>
-      <c r="L61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="6" t="inlineStr"/>
     </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
@@ -3408,8 +3704,13 @@
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr"/>
-      <c r="K62" s="4" t="inlineStr"/>
-      <c r="L62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="4" t="inlineStr"/>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -3454,8 +3755,13 @@
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr"/>
-      <c r="K63" s="6" t="inlineStr"/>
-      <c r="L63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="6" t="inlineStr"/>
     </row>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
@@ -3504,8 +3810,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K64" s="4" t="inlineStr"/>
-      <c r="L64" s="4" t="inlineStr">
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3558,8 +3869,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K65" s="6" t="inlineStr"/>
-      <c r="L65" s="6" t="inlineStr">
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -3612,8 +3928,13 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="K66" s="4" t="inlineStr"/>
-      <c r="L66" s="4" t="inlineStr">
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -3662,8 +3983,13 @@
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr"/>
-      <c r="K67" s="6" t="inlineStr"/>
-      <c r="L67" s="6" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="6" t="inlineStr"/>
     </row>
     <row r="68" ht="32" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
@@ -3708,8 +4034,13 @@
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr"/>
-      <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="4" t="inlineStr"/>
     </row>
     <row r="69" ht="32" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -3754,8 +4085,13 @@
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr"/>
-      <c r="K69" s="6" t="inlineStr"/>
-      <c r="L69" s="6" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="6" t="inlineStr"/>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
@@ -3800,8 +4136,13 @@
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr"/>
-      <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr"/>
     </row>
     <row r="71" ht="32" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -3846,8 +4187,13 @@
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr"/>
-      <c r="K71" s="6" t="inlineStr"/>
-      <c r="L71" s="6" t="inlineStr"/>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="6" t="inlineStr"/>
     </row>
     <row r="72" ht="32" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
@@ -3892,8 +4238,13 @@
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr"/>
-      <c r="K72" s="4" t="inlineStr"/>
-      <c r="L72" s="4" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="4" t="inlineStr"/>
     </row>
     <row r="73" ht="32" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -3938,8 +4289,13 @@
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr"/>
-      <c r="K73" s="6" t="inlineStr"/>
-      <c r="L73" s="6" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="6" t="inlineStr"/>
     </row>
     <row r="74" ht="32" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
@@ -3984,8 +4340,13 @@
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr"/>
-      <c r="K74" s="4" t="inlineStr"/>
-      <c r="L74" s="4" t="inlineStr"/>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="4" t="inlineStr"/>
     </row>
     <row r="75" ht="32" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -4034,8 +4395,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K75" s="6" t="inlineStr"/>
-      <c r="L75" s="6" t="inlineStr">
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -4084,8 +4450,13 @@
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr"/>
-      <c r="K76" s="4" t="inlineStr"/>
-      <c r="L76" s="4" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="4" t="inlineStr"/>
     </row>
     <row r="77" ht="32" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -4130,8 +4501,13 @@
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr"/>
-      <c r="K77" s="6" t="inlineStr"/>
-      <c r="L77" s="6" t="inlineStr"/>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="6" t="inlineStr"/>
     </row>
     <row r="78" ht="32" customHeight="1">
       <c r="A78" s="3" t="inlineStr">
@@ -4176,8 +4552,13 @@
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr"/>
-      <c r="K78" s="4" t="inlineStr"/>
-      <c r="L78" s="4" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="4" t="inlineStr"/>
     </row>
     <row r="79" ht="32" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -4222,8 +4603,13 @@
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr"/>
-      <c r="K79" s="6" t="inlineStr"/>
-      <c r="L79" s="6" t="inlineStr"/>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="6" t="inlineStr"/>
     </row>
     <row r="80" ht="32" customHeight="1">
       <c r="A80" s="3" t="inlineStr">
@@ -4272,8 +4658,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr"/>
-      <c r="L80" s="4" t="inlineStr">
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4322,8 +4713,13 @@
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr"/>
-      <c r="K81" s="6" t="inlineStr"/>
-      <c r="L81" s="6" t="inlineStr"/>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="6" t="inlineStr"/>
     </row>
     <row r="82" ht="32" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
@@ -4368,8 +4764,13 @@
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr"/>
-      <c r="K82" s="4" t="inlineStr"/>
-      <c r="L82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="4" t="inlineStr"/>
     </row>
     <row r="83" ht="32" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
@@ -4414,8 +4815,13 @@
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr"/>
-      <c r="K83" s="6" t="inlineStr"/>
-      <c r="L83" s="6" t="inlineStr"/>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="6" t="inlineStr"/>
     </row>
     <row r="84" ht="32" customHeight="1">
       <c r="A84" s="3" t="inlineStr">
@@ -4460,8 +4866,13 @@
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr"/>
-      <c r="K84" s="4" t="inlineStr"/>
-      <c r="L84" s="4" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="4" t="inlineStr"/>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -4506,8 +4917,13 @@
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr"/>
-      <c r="K85" s="6" t="inlineStr"/>
-      <c r="L85" s="6" t="inlineStr"/>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="6" t="inlineStr"/>
     </row>
     <row r="86" ht="32" customHeight="1">
       <c r="A86" s="3" t="inlineStr">
@@ -4552,8 +4968,13 @@
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr"/>
-      <c r="K86" s="4" t="inlineStr"/>
-      <c r="L86" s="4" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="4" t="inlineStr"/>
     </row>
     <row r="87" ht="32" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -4598,8 +5019,13 @@
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr"/>
-      <c r="K87" s="6" t="inlineStr"/>
-      <c r="L87" s="6" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="6" t="inlineStr"/>
     </row>
     <row r="88" ht="32" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
@@ -4644,8 +5070,13 @@
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr"/>
-      <c r="K88" s="4" t="inlineStr"/>
-      <c r="L88" s="4" t="inlineStr"/>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="4" t="inlineStr"/>
     </row>
     <row r="89" ht="32" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
@@ -4690,8 +5121,13 @@
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr"/>
-      <c r="K89" s="6" t="inlineStr"/>
-      <c r="L89" s="6" t="inlineStr"/>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="6" t="inlineStr"/>
     </row>
     <row r="90" ht="32" customHeight="1">
       <c r="A90" s="3" t="inlineStr">
@@ -4736,8 +5172,13 @@
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr"/>
-      <c r="K90" s="4" t="inlineStr"/>
-      <c r="L90" s="4" t="inlineStr"/>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="4" t="inlineStr"/>
     </row>
     <row r="91" ht="32" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -4782,8 +5223,13 @@
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr"/>
-      <c r="K91" s="6" t="inlineStr"/>
-      <c r="L91" s="6" t="inlineStr"/>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="6" t="inlineStr"/>
     </row>
     <row r="92" ht="32" customHeight="1">
       <c r="A92" s="3" t="inlineStr">
@@ -4828,8 +5274,13 @@
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr"/>
-      <c r="K92" s="4" t="inlineStr"/>
-      <c r="L92" s="4" t="inlineStr"/>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="4" t="inlineStr"/>
     </row>
     <row r="93" ht="32" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
@@ -4874,8 +5325,13 @@
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr"/>
-      <c r="K93" s="6" t="inlineStr"/>
-      <c r="L93" s="6" t="inlineStr"/>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="6" t="inlineStr"/>
     </row>
     <row r="94" ht="32" customHeight="1">
       <c r="A94" s="3" t="inlineStr">
@@ -4920,8 +5376,13 @@
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr"/>
-      <c r="K94" s="4" t="inlineStr"/>
-      <c r="L94" s="4" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="4" t="inlineStr"/>
     </row>
     <row r="95" ht="32" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
@@ -4966,8 +5427,13 @@
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr"/>
-      <c r="K95" s="6" t="inlineStr"/>
-      <c r="L95" s="6" t="inlineStr"/>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="6" t="inlineStr"/>
     </row>
     <row r="96" ht="32" customHeight="1">
       <c r="A96" s="3" t="inlineStr">
@@ -5012,8 +5478,13 @@
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr"/>
-      <c r="K96" s="4" t="inlineStr"/>
-      <c r="L96" s="4" t="inlineStr"/>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="4" t="inlineStr"/>
     </row>
     <row r="97" ht="32" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
@@ -5058,8 +5529,13 @@
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr"/>
-      <c r="K97" s="6" t="inlineStr"/>
-      <c r="L97" s="6" t="inlineStr"/>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="6" t="inlineStr"/>
     </row>
     <row r="98" ht="32" customHeight="1">
       <c r="A98" s="3" t="inlineStr">
@@ -5104,8 +5580,13 @@
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr"/>
-      <c r="K98" s="4" t="inlineStr"/>
-      <c r="L98" s="4" t="inlineStr"/>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="4" t="inlineStr"/>
     </row>
     <row r="99" ht="32" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
@@ -5154,8 +5635,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K99" s="6" t="inlineStr"/>
-      <c r="L99" s="6" t="inlineStr">
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -5204,8 +5690,13 @@
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr"/>
-      <c r="K100" s="4" t="inlineStr"/>
-      <c r="L100" s="4" t="inlineStr"/>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="4" t="inlineStr"/>
     </row>
     <row r="101" ht="32" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
@@ -5250,8 +5741,13 @@
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr"/>
-      <c r="K101" s="6" t="inlineStr"/>
-      <c r="L101" s="6" t="inlineStr"/>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="6" t="inlineStr"/>
     </row>
     <row r="102" ht="32" customHeight="1">
       <c r="A102" s="3" t="inlineStr">
@@ -5296,8 +5792,13 @@
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr"/>
-      <c r="K102" s="4" t="inlineStr"/>
-      <c r="L102" s="4" t="inlineStr"/>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="4" t="inlineStr"/>
     </row>
     <row r="103" ht="32" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
@@ -5346,8 +5847,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K103" s="6" t="inlineStr"/>
-      <c r="L103" s="6" t="inlineStr">
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -5396,8 +5902,13 @@
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr"/>
-      <c r="K104" s="4" t="inlineStr"/>
-      <c r="L104" s="4" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="4" t="inlineStr"/>
     </row>
     <row r="105" ht="32" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
@@ -5446,8 +5957,13 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K105" s="6" t="inlineStr"/>
-      <c r="L105" s="6" t="inlineStr">
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -5496,8 +6012,13 @@
         </is>
       </c>
       <c r="J106" s="4" t="inlineStr"/>
-      <c r="K106" s="4" t="inlineStr"/>
-      <c r="L106" s="4" t="inlineStr"/>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="4" t="inlineStr"/>
     </row>
     <row r="107" ht="32" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
@@ -5542,8 +6063,13 @@
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr"/>
-      <c r="K107" s="6" t="inlineStr"/>
-      <c r="L107" s="6" t="inlineStr"/>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="6" t="inlineStr"/>
     </row>
     <row r="108" ht="32" customHeight="1">
       <c r="A108" s="3" t="inlineStr">
@@ -5592,8 +6118,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K108" s="4" t="inlineStr"/>
-      <c r="L108" s="4" t="inlineStr">
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -5642,8 +6173,13 @@
         </is>
       </c>
       <c r="J109" s="6" t="inlineStr"/>
-      <c r="K109" s="6" t="inlineStr"/>
-      <c r="L109" s="6" t="inlineStr"/>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="6" t="inlineStr"/>
     </row>
     <row r="110" ht="32" customHeight="1">
       <c r="A110" s="3" t="inlineStr">
@@ -5692,8 +6228,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K110" s="4" t="inlineStr"/>
-      <c r="L110" s="4" t="inlineStr">
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -5742,8 +6283,13 @@
         </is>
       </c>
       <c r="J111" s="6" t="inlineStr"/>
-      <c r="K111" s="6" t="inlineStr"/>
-      <c r="L111" s="6" t="inlineStr"/>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="6" t="inlineStr"/>
     </row>
     <row r="112" ht="32" customHeight="1">
       <c r="A112" s="3" t="inlineStr">
@@ -5788,8 +6334,13 @@
         </is>
       </c>
       <c r="J112" s="4" t="inlineStr"/>
-      <c r="K112" s="4" t="inlineStr"/>
-      <c r="L112" s="4" t="inlineStr"/>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="4" t="inlineStr"/>
     </row>
     <row r="113" ht="32" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
@@ -5834,8 +6385,13 @@
         </is>
       </c>
       <c r="J113" s="6" t="inlineStr"/>
-      <c r="K113" s="6" t="inlineStr"/>
-      <c r="L113" s="6" t="inlineStr"/>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="6" t="inlineStr"/>
     </row>
     <row r="114" ht="32" customHeight="1">
       <c r="A114" s="3" t="inlineStr">
@@ -5880,8 +6436,13 @@
         </is>
       </c>
       <c r="J114" s="4" t="inlineStr"/>
-      <c r="K114" s="4" t="inlineStr"/>
-      <c r="L114" s="4" t="inlineStr"/>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="4" t="inlineStr"/>
     </row>
     <row r="115" ht="32" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
@@ -5926,8 +6487,13 @@
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr"/>
-      <c r="K115" s="6" t="inlineStr"/>
-      <c r="L115" s="6" t="inlineStr"/>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="6" t="inlineStr"/>
     </row>
     <row r="116" ht="32" customHeight="1">
       <c r="A116" s="3" t="inlineStr">
@@ -5972,8 +6538,13 @@
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr"/>
-      <c r="K116" s="4" t="inlineStr"/>
-      <c r="L116" s="4" t="inlineStr"/>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="4" t="inlineStr"/>
     </row>
     <row r="117" ht="32" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
@@ -6018,8 +6589,13 @@
         </is>
       </c>
       <c r="J117" s="6" t="inlineStr"/>
-      <c r="K117" s="6" t="inlineStr"/>
-      <c r="L117" s="6" t="inlineStr"/>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="6" t="inlineStr"/>
     </row>
     <row r="118" ht="32" customHeight="1">
       <c r="A118" s="3" t="inlineStr">
@@ -6064,8 +6640,13 @@
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr"/>
-      <c r="K118" s="4" t="inlineStr"/>
-      <c r="L118" s="4" t="inlineStr"/>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="4" t="inlineStr"/>
     </row>
     <row r="119" ht="32" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
@@ -6110,8 +6691,13 @@
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr"/>
-      <c r="K119" s="6" t="inlineStr"/>
-      <c r="L119" s="6" t="inlineStr"/>
+      <c r="K119" s="6" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="6" t="inlineStr"/>
     </row>
     <row r="120" ht="32" customHeight="1">
       <c r="A120" s="3" t="inlineStr">
@@ -6156,8 +6742,13 @@
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr"/>
-      <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="4" t="inlineStr"/>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="4" t="inlineStr"/>
     </row>
     <row r="121" ht="32" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
@@ -6206,8 +6797,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K121" s="6" t="inlineStr"/>
-      <c r="L121" s="6" t="inlineStr">
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -6256,8 +6852,13 @@
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr"/>
-      <c r="K122" s="4" t="inlineStr"/>
-      <c r="L122" s="4" t="inlineStr"/>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="4" t="inlineStr"/>
     </row>
     <row r="123" ht="32" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
@@ -6306,8 +6907,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K123" s="6" t="inlineStr"/>
-      <c r="L123" s="6" t="inlineStr">
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -6356,8 +6962,13 @@
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr"/>
-      <c r="K124" s="4" t="inlineStr"/>
-      <c r="L124" s="4" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="4" t="inlineStr"/>
     </row>
     <row r="125" ht="32" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
@@ -6406,8 +7017,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K125" s="6" t="inlineStr"/>
-      <c r="L125" s="6" t="inlineStr">
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -6456,8 +7072,13 @@
         </is>
       </c>
       <c r="J126" s="4" t="inlineStr"/>
-      <c r="K126" s="4" t="inlineStr"/>
-      <c r="L126" s="4" t="inlineStr"/>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="4" t="inlineStr"/>
     </row>
     <row r="127" ht="32" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
@@ -6503,7 +7124,8 @@
       </c>
       <c r="J127" s="6" t="inlineStr"/>
       <c r="K127" s="6" t="inlineStr"/>
-      <c r="L127" s="6" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="6" t="inlineStr"/>
     </row>
     <row r="128" ht="32" customHeight="1">
       <c r="A128" s="3" t="inlineStr">
@@ -6549,7 +7171,8 @@
       </c>
       <c r="J128" s="4" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr"/>
-      <c r="L128" s="4" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="4" t="inlineStr"/>
     </row>
     <row r="129" ht="32" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
@@ -6594,8 +7217,13 @@
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr"/>
-      <c r="K129" s="6" t="inlineStr"/>
-      <c r="L129" s="6" t="inlineStr"/>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="6" t="inlineStr"/>
     </row>
     <row r="130" ht="48" customHeight="1">
       <c r="A130" s="3" t="inlineStr">
@@ -6640,8 +7268,13 @@
         </is>
       </c>
       <c r="J130" s="4" t="inlineStr"/>
-      <c r="K130" s="4" t="inlineStr"/>
-      <c r="L130" s="4" t="inlineStr"/>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="4" t="inlineStr"/>
     </row>
     <row r="131" ht="48" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
@@ -6690,8 +7323,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K131" s="6" t="inlineStr"/>
-      <c r="L131" s="6" t="inlineStr">
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -6744,8 +7382,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="4" t="inlineStr">
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -6798,8 +7441,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K133" s="6" t="inlineStr"/>
-      <c r="L133" s="6" t="inlineStr">
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="6" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -6852,8 +7500,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K134" s="4" t="inlineStr"/>
-      <c r="L134" s="4" t="inlineStr">
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="4" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
